--- a/public/modelos/biblioteca-v2/PCM-MAN-011_Indicadores-Mensais_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-011_Indicadores-Mensais_R00.xlsx
@@ -2255,7 +2255,7 @@
       <c r="E20" s="29" t="n"/>
       <c r="F20" s="29" t="n"/>
     </row>
-    <row r="21" ht="34" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="B21" s="26" t="n">
         <v>3</v>
       </c>
@@ -2266,13 +2266,13 @@
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>A cada mês, digite horas programadas e de operação, nº de falhas, horas de reparo, PM planejadas e feitas e horas em corretiva e preventiva.</t>
+          <t>A cada mês: horas programadas (do calendário de turnos) e horas de operação = programadas − horas paradas por falha. Falhas e horas de reparo vêm do Registro de falhas (008). Sem falha no mês, digite 0; sem horas programadas, deixe em branco. Falha ainda aberta: conte até o fim do mês e corrija depois. Falha que passa para o mês seguinte: reparo todo no mês em que começou; as horas paradas, divididas por mês.</t>
         </is>
       </c>
       <c r="E21" s="29" t="n"/>
       <c r="F21" s="29" t="n"/>
     </row>
-    <row r="22" ht="34" customHeight="1">
+    <row r="22" ht="46" customHeight="1">
       <c r="B22" s="26" t="n">
         <v>4</v>
       </c>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
-          <t>MTBF, MTTR, disponibilidade, cumprimento da PM e % corretiva saem sozinhos: verde na meta, vermelho fora. Os gráficos mostram a evolução.</t>
+          <t>MTBF = operação ÷ falhas; MTTR = reparo ÷ falhas; disponibilidade = operação ÷ programadas. Sem o divisor (0 falhas ou sem horas) o resultado fica em branco = sem dado, nunca zero. Verde na meta, vermelho fora; os gráficos mostram a evolução.</t>
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
